--- a/hotel_data.xlsx
+++ b/hotel_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rooms" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bookings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="services_catalog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="rooms" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="bookings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="services_catalog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/hotel_data.xlsx
+++ b/hotel_data.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>available</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,94 @@
         <v>4</v>
       </c>
       <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GU-003</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Saad</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>saad@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:16:11.156304</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GU-004</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Arian Zahir</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>arian@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>123123</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>guest</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:29:31.396041</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -914,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,6 +1116,110 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B-94576ED6</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GU-003</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RM-101</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>540</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>GU-003</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:16:44.406707</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SV-002|Airport Transfer|transport|60.0|1|2026-05-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B-F019D110</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GU-004</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RM-102</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>900</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GU-004</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-05-31T22:29:49.306999</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
